--- a/iba/docs/escalation actions worksheet.xlsx
+++ b/iba/docs/escalation actions worksheet.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Bible_study_projects\iba\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0D70A83-5955-4524-BE4A-C880A85FB3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E091DE26-26FA-4A37-951E-39F1B79A41EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7AEB6694-A08E-49E1-807B-C60BA5639946}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Escalations" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="77">
   <si>
     <t>Escalation tool</t>
   </si>
@@ -243,7 +243,25 @@
     <t>DecisionRequired</t>
   </si>
   <si>
-    <r>
+    <t>AnswerRun|ResolveSelfCorrectable|EscalateToDecision</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00008B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>on</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA9A9A9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
       <t>-</t>
     </r>
     <r>
@@ -253,7 +271,135 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>RelatedActivity</t>
+      <t>hold</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA9A9A9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00008B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>in</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA9A9A9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00008B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>progress</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA9A9A9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00008B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>closed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA9A9A9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00008B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>withdraw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA9A9A9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00008B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>supersede</t>
+    </r>
+  </si>
+  <si>
+    <t>review</t>
+  </si>
+  <si>
+    <t>revise</t>
+  </si>
+  <si>
+    <t>approval</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Issue</t>
+  </si>
+  <si>
+    <t>in-progress</t>
+  </si>
+  <si>
+    <t>supercede</t>
+  </si>
+  <si>
+    <t>supersede</t>
+  </si>
+  <si>
+    <t>reject</t>
+  </si>
+  <si>
+    <t>withdraw</t>
+  </si>
+  <si>
+    <t>hold</t>
+  </si>
+  <si>
+    <r>
+      <t>ready</t>
     </r>
     <r>
       <rPr>
@@ -262,16 +408,8 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>-FromID</t>
-  </si>
-  <si>
-    <t>AnswerRun|ResolveSelfCorrectable|EscalateToDecision</t>
-  </si>
-  <si>
+      <t>_</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -279,7 +417,25 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>on</t>
+      <t>for</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00008B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>approval</t>
     </r>
     <r>
       <rPr>
@@ -288,7 +444,7 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>-</t>
+      <t>|</t>
     </r>
     <r>
       <rPr>
@@ -297,7 +453,7 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>hold</t>
+      <t>approved</t>
     </r>
     <r>
       <rPr>
@@ -315,7 +471,7 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>in</t>
+      <t>reject</t>
     </r>
     <r>
       <rPr>
@@ -324,7 +480,7 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>-</t>
+      <t>|</t>
     </r>
     <r>
       <rPr>
@@ -333,7 +489,7 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>progress</t>
+      <t>revise</t>
     </r>
     <r>
       <rPr>
@@ -351,7 +507,7 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>closed</t>
+      <t>noted</t>
     </r>
     <r>
       <rPr>
@@ -369,188 +525,6 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>withdraw</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA9A9A9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00008B"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>supersede</t>
-    </r>
-  </si>
-  <si>
-    <t>review</t>
-  </si>
-  <si>
-    <t>revise</t>
-  </si>
-  <si>
-    <t>approval</t>
-  </si>
-  <si>
-    <t>Task</t>
-  </si>
-  <si>
-    <t>Issue</t>
-  </si>
-  <si>
-    <t>in-progress</t>
-  </si>
-  <si>
-    <t>supercede</t>
-  </si>
-  <si>
-    <t>supersede</t>
-  </si>
-  <si>
-    <t>reject</t>
-  </si>
-  <si>
-    <t>withdraw</t>
-  </si>
-  <si>
-    <t>hold</t>
-  </si>
-  <si>
-    <r>
-      <t>ready</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF333333"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00008B"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>for</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF333333"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00008B"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>approval</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA9A9A9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00008B"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>approved</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA9A9A9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00008B"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>reject</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA9A9A9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00008B"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>revise</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA9A9A9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00008B"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>noted</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA9A9A9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00008B"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
       <t>review|hold</t>
     </r>
   </si>
@@ -576,9 +550,6 @@
     <t>more info</t>
   </si>
   <si>
-    <t>Not related</t>
-  </si>
-  <si>
     <t>issue</t>
   </si>
   <si>
@@ -591,21 +562,9 @@
     <t>completed</t>
   </si>
   <si>
-    <t>This is a test</t>
-  </si>
-  <si>
-    <t>Escalation script testing</t>
-  </si>
-  <si>
-    <t>Set to revise</t>
-  </si>
-  <si>
     <t>Set to ready for approval</t>
   </si>
   <si>
-    <t>set to approved</t>
-  </si>
-  <si>
     <t>Resolution required</t>
   </si>
   <si>
@@ -618,16 +577,37 @@
     <t>Notice</t>
   </si>
   <si>
-    <t>set rejected and supersede</t>
-  </si>
-  <si>
     <t>-State</t>
   </si>
   <si>
-    <t>set to rejected</t>
-  </si>
-  <si>
     <t>set to on hold</t>
+  </si>
+  <si>
+    <t>substantial work has gone into governance, and I am not planning to do a another full sweep of governance</t>
+  </si>
+  <si>
+    <t>taken off hold.   Has this now been cleared</t>
+  </si>
+  <si>
+    <t>not approved, to be redesigned</t>
+  </si>
+  <si>
+    <t>Prose change log</t>
+  </si>
+  <si>
+    <t>Review prose change log to validate it is working correctly</t>
+  </si>
+  <si>
+    <t>section 69 update</t>
+  </si>
+  <si>
+    <t>Align the section  id 69 for programme with the current approach of using CC and API rather than AI and also work in how CC and Researcher is working in colaboration</t>
+  </si>
+  <si>
+    <t>Proceed with review and update</t>
+  </si>
+  <si>
+    <t>seems to be working</t>
   </si>
 </sst>
 </file>
@@ -693,7 +673,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -715,7 +695,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1050,13 +1029,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D0F6153-362F-416E-9FFC-C7AB60768AC1}">
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="31.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="29.28515625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
     <col min="5" max="5" width="13.140625" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" style="2" customWidth="1"/>
     <col min="8" max="8" width="15.42578125" customWidth="1"/>
     <col min="10" max="10" width="14.7109375" customWidth="1"/>
     <col min="11" max="12" width="13" customWidth="1"/>
@@ -1064,22 +1044,22 @@
     <col min="14" max="14" width="22" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -1090,7 +1070,7 @@
       <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="3" t="s">
         <v>29</v>
       </c>
       <c r="H4" s="1" t="s">
@@ -1106,7 +1086,7 @@
         <v>7</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>9</v>
@@ -1117,16 +1097,10 @@
       <c r="O4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="P4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:15" ht="90" x14ac:dyDescent="0.25">
       <c r="E5" s="1"/>
-      <c r="G5" t="s">
+      <c r="G5" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H5" s="5" t="s">
@@ -1136,22 +1110,22 @@
         <v>32</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="107.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="107.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C6" s="2" t="str">
-        <f>D6&amp;" " &amp;$E$4&amp;" "&amp;E6&amp;" "  &amp;$G$4&amp;" '"&amp;G6&amp;"' "&amp;$H$4&amp;" "&amp;H6&amp;" " &amp;$I$4&amp;" "&amp;I6&amp; " " &amp;$K$4 &amp; " " &amp;K6 &amp; " " &amp;$M$4&amp;" '" &amp; M6 &amp; "' " &amp;$N$4&amp;" '" &amp; N6 &amp;"' " &amp; $P$4 &amp; " '" &amp; P6 &amp; "' " &amp; $Q$4 &amp; " '"&amp;Q6&amp;"'"</f>
-        <v>iba\app\ps\Escalation.ps1 -action raise -Question 'title' -ResolutionKind DecisionRequired -Type issue -AssignedTo Researcher -Comment 'assigment' -Context 'more info' -RelatedActivity  'Not related' -FromID '-1'</v>
+        <f>D6&amp;" " &amp;$E$4&amp;" "&amp;E6&amp;" "  &amp;$G$4&amp;" '"&amp;G6&amp;"' "&amp;$H$4&amp;" "&amp;H6&amp;" " &amp;$I$4&amp;" "&amp;I6&amp; " " &amp;$K$4 &amp; " " &amp;K6 &amp; " " &amp;$M$4&amp;" '" &amp; M6 &amp; "' " &amp;$N$4&amp;" '" &amp; N6 &amp;"' "</f>
+        <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action raise -Question 'Prose change log' -ResolutionKind DecisionRequired -Type issue -AssignedTo Researcher -Comment 'Review prose change log to validate it is working correctly' -Context 'more info' </v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
@@ -1159,39 +1133,32 @@
       <c r="E6" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="4" t="s">
-        <v>56</v>
+      <c r="G6" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="H6" t="s">
         <v>35</v>
       </c>
       <c r="I6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="K6" t="s">
         <v>25</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q6" s="4">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="135" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C7" s="2" t="str">
-        <f>D7&amp;" " &amp;$E$4&amp;" "&amp;E7&amp;" "  &amp;$G$4&amp;" '"&amp;G7&amp;"' "&amp;$H$4&amp;" "&amp;H7&amp;" " &amp;$I$4&amp;" "&amp;I7&amp; " " &amp;$K$4 &amp; " " &amp;K7 &amp; " " &amp;$M$4&amp;" '" &amp; M7 &amp; "' " &amp;$N$4&amp;" '" &amp; N7 &amp;"' " &amp; $P$4 &amp; " '" &amp; P7 &amp; "' " &amp; $Q$4 &amp; " '"&amp;Q7&amp;"'"</f>
-        <v>iba\app\ps\Escalation.ps1 -action raise -Question 'title' -ResolutionKind DecisionRequired -Type task -AssignedTo Researcher -Comment 'assigment' -Context 'more info' -RelatedActivity  'Not related' -FromID '-1'</v>
+        <f>D7&amp;" " &amp;$E$4&amp;" "&amp;E7&amp;" "  &amp;$G$4&amp;" '"&amp;G7&amp;"' "&amp;$H$4&amp;" "&amp;H7&amp;" " &amp;$I$4&amp;" "&amp;I7&amp; " " &amp;$K$4 &amp; " " &amp;K7 &amp; " " &amp;$M$4&amp;" '" &amp; M7 &amp; "' " &amp;$N$4&amp;" '" &amp; N7 &amp;"' "</f>
+        <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action raise -Question 'section 69 update' -ResolutionKind DecisionRequired -Type task -AssignedTo Researcher -Comment 'Align the section  id 69 for programme with the current approach of using CC and API rather than AI and also work in how CC and Researcher is working in colaboration' -Context '' </v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
@@ -1199,39 +1166,30 @@
       <c r="E7" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="4" t="s">
-        <v>56</v>
+      <c r="G7" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="H7" t="s">
         <v>35</v>
       </c>
       <c r="I7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="K7" t="s">
         <v>25</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+      <c r="N7" s="8"/>
+    </row>
+    <row r="8" spans="1:15" ht="90" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C8" s="2" t="str">
-        <f>D8&amp;" " &amp;$E$4&amp;" "&amp;E8&amp;" "  &amp;$G$4&amp;" '"&amp;G8&amp;"' "&amp;$H$4&amp;" "&amp;H8&amp;" " &amp;$I$4&amp;" "&amp;I8&amp; " " &amp;$K$4 &amp; " " &amp;K8 &amp; " " &amp;$M$4&amp;" '" &amp; M8 &amp; "' " &amp;$N$4&amp;" '" &amp; N8 &amp;"' " &amp; $P$4 &amp; " '" &amp; P8 &amp; "' " &amp; $Q$4 &amp; " '"&amp;Q8&amp;"'"</f>
-        <v>iba\app\ps\Escalation.ps1 -action raise -Question 'title' -ResolutionKind DecisionRequired -Type notice -AssignedTo Researcher -Comment 'assigment' -Context 'more info' -RelatedActivity  'Not related' -FromID '-1'</v>
+        <f>D8&amp;" " &amp;$E$4&amp;" "&amp;E8&amp;" "  &amp;$G$4&amp;" '"&amp;G8&amp;"' "&amp;$H$4&amp;" "&amp;H8&amp;" " &amp;$I$4&amp;" "&amp;I8&amp; " " &amp;$K$4 &amp; " " &amp;K8 &amp; " " &amp;$M$4&amp;" '" &amp; M8 &amp; "' " &amp;$N$4&amp;" '" &amp; N8 &amp;"' "</f>
+        <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action raise -Question 'title' -ResolutionKind DecisionRequired -Type notice -AssignedTo Researcher -Comment 'assigment' -Context 'more info' </v>
       </c>
       <c r="D8" t="s">
         <v>15</v>
@@ -1239,285 +1197,266 @@
       <c r="E8" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="4" t="s">
-        <v>56</v>
+      <c r="G8" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="H8" t="s">
         <v>35</v>
       </c>
       <c r="I8" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="K8" t="s">
         <v>25</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q8" s="4">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-    </row>
-    <row r="11" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="105" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C11" s="2" t="str">
-        <f>D11&amp;" " &amp;$E$4&amp;" "&amp;E11&amp;" " &amp;$F$4&amp;" "&amp;F11&amp;" "  &amp;$G$4&amp;" '"&amp;G11&amp;"' " &amp;$J$4&amp;" "&amp;J11&amp; " " &amp;$K$4 &amp; " " &amp;K11 &amp; " " &amp;$M$4&amp;" '" &amp; M11 &amp; "' " &amp;$N$4&amp;" '" &amp; N11 &amp;"' " &amp; $P$4 &amp; " '" &amp; P11 &amp; "' " &amp; $Q$4 &amp; " '"&amp;Q11&amp;"'"</f>
-        <v>iba\app\ps\Escalation.ps1 -action update -Id 869 -Question '' -NextAction review -AssignedTo Claude -Comment 'This is a test' -Context 'Escalation script testing' -RelatedActivity  'Not related' -FromID '-1'</v>
+        <f>D11&amp;" " &amp;$E$4&amp;" "&amp;E11&amp;" " &amp;$F$4&amp;" "&amp;F11&amp;" "  &amp;$H$4&amp;" "&amp;H11&amp;" " &amp;$J$4&amp;" "&amp;J11&amp; " " &amp;$K$4 &amp; " " &amp;K11 &amp; " " &amp;$L$4 &amp; " " &amp;L11 &amp; " " &amp;$M$4&amp;" '" &amp; M11 &amp; "' " &amp;$N$4&amp;" '" &amp; N11 &amp;"' "</f>
+        <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action update -Id 932 -ResolutionKind DecisionRequired -NextAction review -AssignedTo Claude -State in-progress -Comment 'Proceed with review and update' -Context '' </v>
       </c>
       <c r="D11" t="s">
         <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F11" s="4">
-        <v>869</v>
+        <v>932</v>
+      </c>
+      <c r="H11" t="s">
+        <v>35</v>
       </c>
       <c r="J11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K11" t="s">
         <v>8</v>
       </c>
       <c r="L11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="N11" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q11" s="4">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="N11" s="8"/>
+    </row>
+    <row r="12" spans="1:15" ht="105" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C12" s="2" t="str">
-        <f>D12&amp;" " &amp;$E$4&amp;" "&amp;E12&amp;" " &amp;$F$4&amp;" "&amp;F12&amp;" "  &amp;$G$4&amp;" '"&amp;G12&amp;"' " &amp;$J$4&amp;" "&amp;J12&amp; " " &amp;$K$4 &amp; " " &amp;K12 &amp; " " &amp;$M$4&amp;" '" &amp; M12 &amp; "' " &amp;$N$4&amp;" '" &amp; N12 &amp;"' " &amp; $P$4 &amp; " '" &amp; P12 &amp; "' " &amp; $Q$4 &amp; " '"&amp;Q12&amp;"'"</f>
-        <v>iba\app\ps\Escalation.ps1 -action update -Id 869 -Question '' -NextAction revise -AssignedTo Claude -Comment 'Set to revise' -Context '' -RelatedActivity  '' -FromID ''</v>
+        <f>D12&amp;" " &amp;$E$4&amp;" "&amp;E12&amp;" " &amp;$F$4&amp;" "&amp;F12&amp;" "  &amp;$H$4&amp;" "&amp;H12&amp;" " &amp;$J$4&amp;" "&amp;J12&amp; " " &amp;$K$4 &amp; " " &amp;K12 &amp; " " &amp;$L$4 &amp; " " &amp;L12 &amp; " " &amp;$M$4&amp;" '" &amp; M12 &amp; "' " &amp;$N$4&amp;" '" &amp; N12 &amp;"' "</f>
+        <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action update -Id 768 -ResolutionKind DecisionRequired -NextAction revise -AssignedTo Claude -State in-progress -Comment 'taken off hold.   Has this now been cleared' -Context '' </v>
       </c>
       <c r="D12" t="s">
         <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F12" s="4">
-        <v>869</v>
+        <v>768</v>
+      </c>
+      <c r="H12" t="s">
+        <v>35</v>
       </c>
       <c r="J12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K12" t="s">
         <v>8</v>
       </c>
       <c r="L12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="N12" s="8"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-    </row>
-    <row r="13" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:15" ht="120" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C13" s="2" t="str">
-        <f>D13&amp;" " &amp;$E$4&amp;" "&amp;E13&amp;" " &amp;$F$4&amp;" "&amp;F13&amp;" "  &amp;$G$4&amp;" '"&amp;G13&amp;"' " &amp;$J$4&amp;" "&amp;J13&amp; " " &amp;$K$4 &amp; " " &amp;K13 &amp; " " &amp;$M$4&amp;" '" &amp; M13 &amp; "' " &amp;$N$4&amp;" '" &amp; N13 &amp;"' " &amp;$O$4 &amp; " '"&amp; O13 &amp;"'" &amp; $P$4 &amp; " '" &amp; P13 &amp; "' " &amp; $Q$4 &amp; " '"&amp;Q13&amp;"'"</f>
-        <v>iba\app\ps\Escalation.ps1 -action update -Id 869 -Question '' -NextAction ready_for_approval -AssignedTo Researcher -Comment 'Set to ready for approval' -Context '' -Resolution 'Resolution required'-RelatedActivity  '' -FromID ''</v>
+        <f>D13&amp;" " &amp;$E$4&amp;" "&amp;E13&amp;" " &amp;$F$4&amp;" "&amp;F13&amp;" "  &amp;$H$4&amp;" "&amp;H13&amp;" " &amp;$J$4&amp;" "&amp;J13&amp; " " &amp;$K$4 &amp; " " &amp;K13 &amp; " "&amp;$L$4 &amp; " " &amp;L13 &amp; " " &amp;$M$4&amp;" '" &amp; M13 &amp; "' " &amp;$N$4&amp;" '" &amp; N13 &amp;"' " &amp;$O$4 &amp; " '"&amp; O13 &amp;"'"</f>
+        <v>iba\app\ps\Escalation.ps1 -action update -Id 921 -ResolutionKind DecisionRequired -NextAction ready_for_approval -AssignedTo Researcher -State in-progress -Comment 'Set to ready for approval' -Context '' -Resolution 'Resolution required'</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F13" s="4">
-        <v>869</v>
+        <v>921</v>
+      </c>
+      <c r="H13" t="s">
+        <v>35</v>
       </c>
       <c r="J13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K13" t="s">
         <v>25</v>
       </c>
       <c r="L13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="N13" s="8"/>
       <c r="O13" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-    </row>
-    <row r="14" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="105" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C14" s="2" t="str">
-        <f>D14&amp;" " &amp;$E$4&amp;" "&amp;E14&amp;" " &amp;$F$4&amp;" "&amp;F14&amp;" "  &amp;$G$4&amp;" '"&amp;G14&amp;"' " &amp;$J$4&amp;" "&amp;J14&amp; " " &amp;$K$4 &amp; " " &amp;K14 &amp; " " &amp;$M$4&amp;" '" &amp; M14 &amp; "' " &amp;$N$4&amp;" '" &amp; N14 &amp;"' " &amp; $P$4 &amp; " '" &amp; P14 &amp; "' " &amp; $Q$4 &amp; " '"&amp;Q14&amp;"'"</f>
-        <v>iba\app\ps\Escalation.ps1 -action update -Id 869 -Question '' -NextAction approved -AssignedTo Researcher -Comment 'set to approved' -Context '' -RelatedActivity  '' -FromID ''</v>
+        <f>D14&amp;" " &amp;$E$4&amp;" "&amp;E14&amp;" " &amp;$F$4&amp;" "&amp;F14&amp;" "  &amp;$H$4&amp;" "&amp;H14&amp;" " &amp;$J$4&amp;" "&amp;J14&amp; " " &amp;$K$4 &amp; " " &amp;K14 &amp; " "&amp;$L$4 &amp; " " &amp;L14 &amp; " " &amp;$M$4&amp;" '" &amp; M14 &amp; "' " &amp;$N$4&amp;" '" &amp; N14 &amp;"' " &amp;$O$4 &amp; " '"&amp; O14 &amp;"'"</f>
+        <v>iba\app\ps\Escalation.ps1 -action update -Id 931 -ResolutionKind DecisionRequired -NextAction approved -AssignedTo Researcher -State completed -Comment 'seems to be working' -Context '' -Resolution ''</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F14" s="4">
-        <v>869</v>
+        <v>931</v>
+      </c>
+      <c r="H14" t="s">
+        <v>35</v>
       </c>
       <c r="J14" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="K14" t="s">
         <v>25</v>
       </c>
       <c r="L14" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="N14" s="8"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-    </row>
-    <row r="15" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:15" ht="135" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C15" s="2" t="str">
-        <f>D15&amp;" " &amp;$E$4&amp;" "&amp;E15&amp;" " &amp;$F$4&amp;" "&amp;F15&amp;" "  &amp;$G$4&amp;" '"&amp;G15&amp;"' " &amp;$J$4&amp;" "&amp;J15&amp; " " &amp;$K$4 &amp; " " &amp;K15 &amp; " "&amp; $L$4 &amp; " " &amp;L15 &amp;" "  &amp;$M$4&amp;" '" &amp; M15 &amp; "' " &amp;$N$4&amp;" '" &amp; N15 &amp;"' " &amp; $P$4 &amp; " '" &amp; P15 &amp; "' " &amp; $Q$4 &amp; " '"&amp;Q15&amp;"'"</f>
-        <v>iba\app\ps\Escalation.ps1 -action update -Id 870 -Question '' -NextAction reject -AssignedTo Claude -State supersede -Comment 'set rejected and supersede' -Context '' -RelatedActivity  '' -FromID ''</v>
+        <f>D15&amp;" " &amp;$E$4&amp;" "&amp;E15&amp;" " &amp;$F$4&amp;" "&amp;F15&amp;" "  &amp;$H$4&amp;" "&amp;H15&amp;" " &amp;$J$4&amp;" "&amp;J15&amp; " " &amp;$K$4 &amp; " " &amp;K15 &amp; " "&amp;$L$4 &amp; " " &amp;L15 &amp; " " &amp;$M$4&amp;" '" &amp; M15 &amp; "' " &amp;$N$4&amp;" '" &amp; N15 &amp;"' " &amp;$O$4 &amp; " '"&amp; O15 &amp;"'"</f>
+        <v>iba\app\ps\Escalation.ps1 -action update -Id 9 -ResolutionKind  -NextAction reject -AssignedTo Claude -State supersede -Comment 'substantial work has gone into governance, and I am not planning to do a another full sweep of governance' -Context '' -Resolution ''</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F15" s="4">
-        <v>870</v>
+        <v>9</v>
       </c>
       <c r="J15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K15" t="s">
         <v>8</v>
       </c>
       <c r="L15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="N15" s="8"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
-    </row>
-    <row r="16" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:15" ht="105" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C16" s="2" t="str">
-        <f>D16&amp;" " &amp;$E$4&amp;" "&amp;E16&amp;" " &amp;$F$4&amp;" "&amp;F16&amp;" "  &amp;$G$4&amp;" '"&amp;G16&amp;"' " &amp;$J$4&amp;" "&amp;J16&amp; " " &amp;$K$4 &amp; " " &amp;K16 &amp; " "&amp; $L$4 &amp; " " &amp;L16 &amp;" "  &amp;$M$4&amp;" '" &amp; M16 &amp; "' " &amp;$N$4&amp;" '" &amp; N16 &amp;"' " &amp; $P$4 &amp; " '" &amp; P16 &amp; "' " &amp; $Q$4 &amp; " '"&amp;Q16&amp;"'"</f>
-        <v>iba\app\ps\Escalation.ps1 -action update -Id 873 -Question '' -NextAction reject -AssignedTo Claude -State withdraw -Comment 'set to rejected' -Context '' -RelatedActivity  '' -FromID ''</v>
+        <f>D16&amp;" " &amp;$E$4&amp;" "&amp;E16&amp;" " &amp;$F$4&amp;" "&amp;F16&amp;" "  &amp;$H$4&amp;" "&amp;H16&amp;" " &amp;$J$4&amp;" "&amp;J16&amp; " " &amp;$K$4 &amp; " " &amp;K16 &amp; " "&amp;$L$4 &amp; " " &amp;L16 &amp; " " &amp;$M$4&amp;" '" &amp; M16 &amp; "' " &amp;$N$4&amp;" '" &amp; N16 &amp;"' " &amp;$O$4 &amp; " '"&amp; O16 &amp;"'"</f>
+        <v>iba\app\ps\Escalation.ps1 -action update -Id 912 -ResolutionKind  -NextAction reject -AssignedTo Claude -State withdraw -Comment 'not approved, to be redesigned' -Context '' -Resolution ''</v>
       </c>
       <c r="D16" t="s">
         <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F16" s="4">
-        <v>873</v>
+        <v>912</v>
       </c>
       <c r="J16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K16" t="s">
         <v>8</v>
       </c>
       <c r="L16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="N16" s="8"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
-    </row>
-    <row r="17" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:15" ht="90" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C17" s="2" t="str">
-        <f>D17&amp;" " &amp;$E$4&amp;" "&amp;E17&amp;" " &amp;$F$4&amp;" "&amp;F17&amp;" "  &amp;$G$4&amp;" '"&amp;G17&amp;"' " &amp;$K$4 &amp; " " &amp;K17&amp; " "&amp;$L$4 &amp; " " &amp;L17 &amp; " " &amp;$M$4&amp;" '" &amp; M17 &amp; "' " &amp;$N$4&amp;" '" &amp; N17 &amp;"' " &amp; $P$4 &amp; " '" &amp; P17 &amp; "' " &amp; $Q$4 &amp; " '"&amp;Q17&amp;"'"</f>
-        <v>iba\app\ps\Escalation.ps1 -action update -Id 874 -Question '' -AssignedTo Researcher -State on-hold -Comment 'set to on hold' -Context '' -RelatedActivity  '' -FromID ''</v>
+        <f>D17&amp;" " &amp;$E$4&amp;" "&amp;E17&amp;" " &amp;$F$4&amp;" "&amp;F17&amp;" "  &amp;$H$4&amp;" "&amp;H17&amp;" " &amp;$J$4&amp;" "&amp;J17&amp; " " &amp;$K$4 &amp; " " &amp;K17 &amp; " "&amp;$L$4 &amp; " " &amp;L17 &amp; " " &amp;$M$4&amp;" '" &amp; M17 &amp; "' " &amp;$N$4&amp;" '" &amp; N17 &amp;"' " &amp;$O$4 &amp; " '"&amp; O17 &amp;"'"</f>
+        <v>iba\app\ps\Escalation.ps1 -action update -Id 874 -ResolutionKind  -NextAction revise -AssignedTo Researcher -State on-hold -Comment 'set to on hold' -Context '' -Resolution ''</v>
       </c>
       <c r="D17" t="s">
         <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F17" s="4">
         <v>874</v>
       </c>
       <c r="J17" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K17" t="s">
         <v>25</v>
       </c>
       <c r="L17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="N17" s="8"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1535,7 +1474,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -1550,12 +1489,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>12</v>
       </c>
@@ -1571,7 +1510,7 @@
       <c r="F27" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G27" s="1"/>
+      <c r="G27" s="3"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1" t="s">
@@ -1588,15 +1527,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" ht="75" x14ac:dyDescent="0.25">
       <c r="E28" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>21</v>
       </c>

--- a/iba/docs/escalation actions worksheet.xlsx
+++ b/iba/docs/escalation actions worksheet.xlsx
@@ -379,13 +379,13 @@
     <t>Task</t>
   </si>
   <si>
-    <t>section 69 update</t>
+    <t>Explore existing cluster work</t>
   </si>
   <si>
     <t>task</t>
   </si>
   <si>
-    <t>Align the section  id 69 for programme with the current approach of using CC and API rather than AI and also work in how CC and Researcher is working in colaboration</t>
+    <t>The objective is to explore and assess the existing cluster work to determine how much, and in what format can it be harvested and augmented to complete the cluster analysis</t>
   </si>
   <si>
     <t>Notice</t>
@@ -415,7 +415,7 @@
     <t>in-progress</t>
   </si>
   <si>
-    <t>proceed to prepare for approval</t>
+    <t>the initial assesment will be on M08 C:\Bible_study_projects\_analytics\clusters\M08-Pride start off by summarising what is in the folder and extract everything from the DB about M08.  all files must go back on this folder, not in another place.</t>
   </si>
   <si>
     <t>revise</t>
@@ -1220,7 +1220,7 @@
         <v>31</v>
       </c>
       <c r="C7" s="10">
-        <f>D7&amp;" " &amp;$E$4&amp;" "&amp;E7&amp;" "  &amp;$G$4&amp;" '"&amp;G7&amp;"' "&amp;$H$4&amp;" "&amp;H7&amp;" " &amp;$I$4&amp;" "&amp;I7&amp; " " &amp;$K$4 &amp; " " &amp;K7 &amp; " " &amp;$M$4&amp;" '" &amp; M7 &amp; "' " &amp;$N$4&amp;" '" &amp; N7 &amp;"' "</f>
+        <f>D7&amp;" " &amp;$E$4&amp;" "&amp;E7&amp;" "  &amp;$G$4&amp;" ' "&amp;G7&amp;" ' "&amp;$H$4&amp;" "&amp;H7&amp;" " &amp;$I$4&amp;" "&amp;I7&amp; " " &amp;$K$4 &amp; " " &amp;K7 &amp; " " &amp;$M$4&amp;" ' " &amp; M7 &amp; " ' " &amp;$N$4&amp;" ' " &amp; N7 &amp;" ' "</f>
       </c>
       <c r="D7" s="2" t="s">
         <v>23</v>
@@ -1328,7 +1328,7 @@
         <v>40</v>
       </c>
       <c r="C11" s="10">
-        <f>D11&amp;" " &amp;$E$4&amp;" "&amp;E11&amp;" " &amp;$F$4&amp;" "&amp;F11&amp;" "  &amp;$H$4&amp;" "&amp;H11&amp;" " &amp;$J$4&amp;" "&amp;J11&amp; " " &amp;$K$4 &amp; " " &amp;K11 &amp; " " &amp;$L$4 &amp; " " &amp;L11 &amp; " " &amp;$M$4&amp;" '" &amp; M11 &amp; "' " &amp;$N$4&amp;" '" &amp; N11 &amp;"' "</f>
+        <f>D11&amp;" " &amp;$E$4&amp;" "&amp;E11&amp;" " &amp;$F$4&amp;" "&amp;F11&amp;" "  &amp;$H$4&amp;" "&amp;H11&amp;" " &amp;$J$4&amp;" "&amp;J11&amp; " " &amp;$K$4 &amp; " " &amp;K11 &amp; " " &amp;$L$4 &amp; " " &amp;L11 &amp; " " &amp;$M$4&amp;" ' " &amp; M11 &amp; " ' " &amp;$N$4&amp;" ' " &amp; N11 &amp;" ' "</f>
       </c>
       <c r="D11" s="1" t="s">
         <v>23</v>
@@ -1337,7 +1337,7 @@
         <v>41</v>
       </c>
       <c r="F11" s="12">
-        <v>935</v>
+        <v>1005</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">

--- a/iba/docs/escalation actions worksheet.xlsx
+++ b/iba/docs/escalation actions worksheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="81">
   <si>
     <t>Escalation tool</t>
   </si>
@@ -379,13 +379,18 @@
     <t>Task</t>
   </si>
   <si>
-    <t>Explore existing cluster work</t>
+    <t>create ps tool to work with catelogue</t>
   </si>
   <si>
     <t>task</t>
   </si>
   <si>
-    <t>The objective is to explore and assess the existing cluster work to determine how much, and in what format can it be harvested and augmented to complete the cluster analysis</t>
+    <t>The catelogue is the framework used for cluster analysis.  This ps method aim at allowing full CRUD for the tables associated with the catelogue, and also reporting from various angles</t>
+  </si>
+  <si>
+    <t>Previously catelogue work was done with scripts created and modified on demand. 
+The catelogue tables are in the bible_research_db
+The operation functionality around the catelogue must be in IBA_db, fully compliant with governance.</t>
   </si>
   <si>
     <t>Notice</t>
@@ -415,7 +420,7 @@
     <t>in-progress</t>
   </si>
   <si>
-    <t>the initial assesment will be on M08 C:\Bible_study_projects\_analytics\clusters\M08-Pride start off by summarising what is in the folder and extract everything from the DB about M08.  all files must go back on this folder, not in another place.</t>
+    <t>these config errors will resolve when 784 is completed, and this could take a while. I am leaving it here so the system will not duplicate the same error</t>
   </si>
   <si>
     <t>revise</t>
@@ -445,7 +450,7 @@
     <t>completed</t>
   </si>
   <si>
-    <t>update config</t>
+    <t>noted correction</t>
   </si>
   <si>
     <t>supercede</t>
@@ -493,7 +498,16 @@
     <t>Despatcher-tied</t>
   </si>
   <si>
-    <t>Concatenation</t>
+    <t>-RunId</t>
+  </si>
+  <si>
+    <t>-AnsweredBy</t>
+  </si>
+  <si>
+    <t>'-ShortDescription</t>
+  </si>
+  <si>
+    <t>'-Source</t>
   </si>
   <si>
     <t>-Decision</t>
@@ -593,7 +607,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -604,6 +618,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -673,10 +693,58 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general" wrapText="1"/>
@@ -685,45 +753,6 @@
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
   </cellXfs>
@@ -1031,21 +1060,21 @@
   <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="15" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="15" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="16" width="31.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="15" width="14.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="16" width="13.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="16" width="17.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="16" width="15.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="16" width="14.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="15" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="16" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="16" width="24.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="16" width="22.005" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="18" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="18" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="18" width="31.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="18" width="14.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="18" width="13.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="18" width="17.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="18" width="15.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="18" width="14.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="18" width="13.005" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="18" width="13.005" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="18" width="24.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="18" width="22.005" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -1065,7 +1094,7 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
-      <c r="O1" s="1"/>
+      <c r="O1" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1"/>
@@ -1082,9 +1111,9 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="O2" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="31.5">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1101,14 +1130,14 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
-      <c r="O3" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="4">
+      <c r="O3" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5" customFormat="1" s="5">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -1117,10 +1146,10 @@
       <c r="E4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="H4" s="2" t="s">
@@ -1138,51 +1167,51 @@
       <c r="L4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="6" t="s">
         <v>14</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="87" customFormat="1" s="4">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="87" customFormat="1" s="5">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="5" t="s">
+      <c r="F5" s="8"/>
+      <c r="G5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K5" s="2"/>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="11" t="s">
         <v>20</v>
       </c>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="95.25" customFormat="1" s="4">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="100.5" customFormat="1" s="5">
       <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="12">
         <f>D6&amp;" " &amp;$E$4&amp;" "&amp;E6&amp;" "  &amp;$G$4&amp;" '"&amp;G6&amp;"' "&amp;$H$4&amp;" "&amp;H6&amp;" " &amp;$I$4&amp;" "&amp;I6&amp; " " &amp;$K$4 &amp; " " &amp;K6 &amp; " " &amp;$M$4&amp;" '" &amp; M6 &amp; "' " &amp;$N$4&amp;" '" &amp; N6 &amp;"' "</f>
       </c>
       <c r="D6" s="2" t="s">
@@ -1191,8 +1220,8 @@
       <c r="E6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="11" t="s">
+      <c r="F6" s="8"/>
+      <c r="G6" s="13" t="s">
         <v>25</v>
       </c>
       <c r="H6" s="2" t="s">
@@ -1206,20 +1235,20 @@
         <v>28</v>
       </c>
       <c r="L6" s="2"/>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="11" t="s">
+      <c r="N6" s="13" t="s">
         <v>30</v>
       </c>
       <c r="O6" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="133.5" customFormat="1" s="4">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="154.5" customFormat="1" s="5">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="12">
         <f>D7&amp;" " &amp;$E$4&amp;" "&amp;E7&amp;" "  &amp;$G$4&amp;" ' "&amp;G7&amp;" ' "&amp;$H$4&amp;" "&amp;H7&amp;" " &amp;$I$4&amp;" "&amp;I7&amp; " " &amp;$K$4 &amp; " " &amp;K7 &amp; " " &amp;$M$4&amp;" ' " &amp; M7 &amp; " ' " &amp;$N$4&amp;" ' " &amp; N7 &amp;" ' "</f>
       </c>
       <c r="D7" s="2" t="s">
@@ -1228,8 +1257,8 @@
       <c r="E7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="11" t="s">
+      <c r="F7" s="8"/>
+      <c r="G7" s="13" t="s">
         <v>32</v>
       </c>
       <c r="H7" s="2" t="s">
@@ -1243,18 +1272,20 @@
         <v>28</v>
       </c>
       <c r="L7" s="2"/>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="N7" s="11"/>
+      <c r="N7" s="13" t="s">
+        <v>35</v>
+      </c>
       <c r="O7" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="69.75" customFormat="1" s="4">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="87" customFormat="1" s="5">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="10">
+        <v>36</v>
+      </c>
+      <c r="C8" s="12">
         <f>D8&amp;" " &amp;$E$4&amp;" "&amp;E8&amp;" "  &amp;$G$4&amp;" '"&amp;G8&amp;"' "&amp;$H$4&amp;" "&amp;H8&amp;" " &amp;$I$4&amp;" "&amp;I8&amp; " " &amp;$K$4 &amp; " " &amp;K8 &amp; " " &amp;$M$4&amp;" '" &amp; M8 &amp; "' " &amp;$N$4&amp;" '" &amp; N8 &amp;"' "</f>
       </c>
       <c r="D8" s="2" t="s">
@@ -1263,25 +1294,25 @@
       <c r="E8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="11" t="s">
-        <v>36</v>
+      <c r="F8" s="8"/>
+      <c r="G8" s="13" t="s">
+        <v>37</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
         <v>28</v>
       </c>
       <c r="L8" s="2"/>
-      <c r="M8" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="N8" s="11" t="s">
+      <c r="M8" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="N8" s="13" t="s">
         <v>30</v>
       </c>
       <c r="O8" s="2"/>
@@ -1301,7 +1332,7 @@
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
-      <c r="O9" s="1"/>
+      <c r="O9" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="1"/>
@@ -1318,26 +1349,26 @@
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
-      <c r="O10" s="1"/>
+      <c r="O10" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="82.5">
       <c r="A11" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="10">
+        <v>41</v>
+      </c>
+      <c r="C11" s="12">
         <f>D11&amp;" " &amp;$E$4&amp;" "&amp;E11&amp;" " &amp;$F$4&amp;" "&amp;F11&amp;" "  &amp;$H$4&amp;" "&amp;H11&amp;" " &amp;$J$4&amp;" "&amp;J11&amp; " " &amp;$K$4 &amp; " " &amp;K11 &amp; " " &amp;$L$4 &amp; " " &amp;L11 &amp; " " &amp;$M$4&amp;" ' " &amp; M11 &amp; " ' " &amp;$N$4&amp;" ' " &amp; N11 &amp;" ' "</f>
       </c>
       <c r="D11" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="12">
-        <v>1005</v>
+        <v>42</v>
+      </c>
+      <c r="F11" s="14">
+        <v>1008</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
@@ -1345,35 +1376,35 @@
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M11" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="N11" s="11"/>
-      <c r="O11" s="1"/>
+      <c r="M11" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="N11" s="13"/>
+      <c r="O11" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="82.5">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="10">
+        <v>46</v>
+      </c>
+      <c r="C12" s="12">
         <f>D12&amp;" " &amp;$E$4&amp;" "&amp;E12&amp;" " &amp;$F$4&amp;" "&amp;F12&amp;" "  &amp;$H$4&amp;" "&amp;H12&amp;" " &amp;$J$4&amp;" "&amp;J12&amp; " " &amp;$K$4 &amp; " " &amp;K12 &amp; " " &amp;$L$4 &amp; " " &amp;L12 &amp; " " &amp;$M$4&amp;" '" &amp; M12 &amp; "' " &amp;$N$4&amp;" '" &amp; N12 &amp;"' "</f>
       </c>
       <c r="D12" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" s="12">
+        <v>42</v>
+      </c>
+      <c r="F12" s="14">
         <v>768</v>
       </c>
       <c r="G12" s="2"/>
@@ -1382,35 +1413,35 @@
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="N12" s="11"/>
-      <c r="O12" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="M12" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="N12" s="13"/>
+      <c r="O12" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="108">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="10">
+        <v>48</v>
+      </c>
+      <c r="C13" s="12">
         <f>D13&amp;" " &amp;$E$4&amp;" "&amp;E13&amp;" " &amp;$F$4&amp;" "&amp;F13&amp;" "  &amp;$H$4&amp;" "&amp;H13&amp;" " &amp;$J$4&amp;" "&amp;J13&amp; " " &amp;$K$4 &amp; " " &amp;K13 &amp; " "&amp;$L$4 &amp; " " &amp;L13 &amp; " " &amp;$M$4&amp;" '" &amp; M13 &amp; "' " &amp;$N$4&amp;" '" &amp; N13 &amp;"' " &amp;$O$4 &amp; " '"&amp; O13 &amp;"'"</f>
       </c>
       <c r="D13" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" s="12">
+        <v>42</v>
+      </c>
+      <c r="F13" s="14">
         <v>921</v>
       </c>
       <c r="G13" s="2"/>
@@ -1419,38 +1450,38 @@
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>28</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="N13" s="11"/>
-      <c r="O13" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="M13" s="13" t="s">
         <v>50</v>
+      </c>
+      <c r="N13" s="13"/>
+      <c r="O13" s="15" t="s">
+        <v>51</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="95.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="10">
-        <f>D14&amp;" " &amp;$E$4&amp;" "&amp;E14&amp;" " &amp;$F$4&amp;" "&amp;F14&amp;" "  &amp;$H$4&amp;" "&amp;H14&amp;" " &amp;$J$4&amp;" "&amp;J14&amp; " " &amp;$K$4 &amp; " " &amp;K14 &amp; " "&amp;$L$4 &amp; " " &amp;L14 &amp; " " &amp;$M$4&amp;" '" &amp; M14 &amp; "' " </f>
+        <v>52</v>
+      </c>
+      <c r="C14" s="12">
+        <f>D14&amp;" " &amp;$E$4&amp;" "&amp;E14&amp;" " &amp;$F$4&amp;" "&amp;F14&amp;" "  &amp;$H$4&amp;" "&amp;H14&amp;" " &amp;$J$4&amp;" "&amp;J14&amp; " " &amp;$K$4 &amp; " " &amp;K14 &amp; " "&amp;$L$4 &amp; " " &amp;L14 &amp; " " &amp;$M$4&amp;" ' " &amp; M14 &amp; " ' " </f>
       </c>
       <c r="D14" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="12">
-        <v>934</v>
+        <v>42</v>
+      </c>
+      <c r="F14" s="14">
+        <v>1009</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2" t="s">
@@ -1458,124 +1489,124 @@
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M14" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="N14" s="11"/>
-      <c r="O14" s="1"/>
+      <c r="M14" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="N14" s="13"/>
+      <c r="O14" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="108">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="10">
+        <v>56</v>
+      </c>
+      <c r="C15" s="12">
         <f>D15&amp;" " &amp;$E$4&amp;" "&amp;E15&amp;" " &amp;$F$4&amp;" "&amp;F15&amp;" "  &amp;$H$4&amp;" "&amp;H15&amp;" " &amp;$J$4&amp;" "&amp;J15&amp; " " &amp;$K$4 &amp; " " &amp;K15 &amp; " "&amp;$L$4 &amp; " " &amp;L15 &amp; " " &amp;$M$4&amp;" '" &amp; M15 &amp; "' " &amp;$N$4&amp;" '" &amp; N15 &amp;"' " &amp;$O$4 &amp; " '"&amp; O15 &amp;"'"</f>
       </c>
       <c r="D15" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" s="12">
+        <v>42</v>
+      </c>
+      <c r="F15" s="14">
         <v>9</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="M15" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="N15" s="11"/>
-      <c r="O15" s="1"/>
+      <c r="M15" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="82.5">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" s="10">
+        <v>57</v>
+      </c>
+      <c r="C16" s="12">
         <f>D16&amp;" " &amp;$E$4&amp;" "&amp;E16&amp;" " &amp;$F$4&amp;" "&amp;F16&amp;" "  &amp;$H$4&amp;" "&amp;H16&amp;" " &amp;$J$4&amp;" "&amp;J16&amp; " " &amp;$K$4 &amp; " " &amp;K16 &amp; " "&amp;$L$4 &amp; " " &amp;L16 &amp; " " &amp;$M$4&amp;" '" &amp; M16 &amp; "' " &amp;$N$4&amp;" '" &amp; N16 &amp;"' " &amp;$O$4 &amp; " '"&amp; O16 &amp;"'"</f>
       </c>
       <c r="D16" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" s="12">
+        <v>42</v>
+      </c>
+      <c r="F16" s="14">
         <v>912</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="M16" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="N16" s="11"/>
-      <c r="O16" s="1"/>
+      <c r="M16" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="N16" s="13"/>
+      <c r="O16" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="82.5">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" s="10">
+        <v>62</v>
+      </c>
+      <c r="C17" s="12">
         <f>D17&amp;" " &amp;$E$4&amp;" "&amp;E17&amp;" " &amp;$F$4&amp;" "&amp;F17&amp;" "  &amp;$H$4&amp;" "&amp;H17&amp;" " &amp;$J$4&amp;" "&amp;J17&amp; " " &amp;$K$4 &amp; " " &amp;K17 &amp; " "&amp;$L$4 &amp; " " &amp;L17 &amp; " " &amp;$M$4&amp;" '" &amp; M17 &amp; "' " &amp;$N$4&amp;" '" &amp; N17 &amp;"' " &amp;$O$4 &amp; " '"&amp; O17 &amp;"'"</f>
       </c>
       <c r="D17" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" s="12">
+        <v>42</v>
+      </c>
+      <c r="F17" s="14">
         <v>874</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>28</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="M17" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="N17" s="11"/>
-      <c r="O17" s="1"/>
+      <c r="M17" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="N17" s="13"/>
+      <c r="O17" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="1"/>
@@ -1592,11 +1623,11 @@
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
-      <c r="O18" s="1"/>
+      <c r="O18" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="2"/>
@@ -1611,7 +1642,7 @@
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
-      <c r="O19" s="1"/>
+      <c r="O19" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="1"/>
@@ -1628,23 +1659,23 @@
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
-      <c r="O20" s="1"/>
+      <c r="O20" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B21" s="1"/>
-      <c r="C21" s="10">
+      <c r="C21" s="12">
         <f>D21&amp;" " &amp;$E$4&amp;" "&amp;E21&amp;" " &amp;$F$4 &amp; " " &amp;F21</f>
       </c>
       <c r="D21" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F21" s="14">
+        <v>67</v>
+      </c>
+      <c r="F21" s="16">
         <v>851</v>
       </c>
       <c r="G21" s="2"/>
@@ -1655,7 +1686,7 @@
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
-      <c r="O21" s="1"/>
+      <c r="O21" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="1"/>
@@ -1672,23 +1703,23 @@
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
-      <c r="O22" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75" customFormat="1" s="4">
+      <c r="O22" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75" customFormat="1" s="5">
       <c r="A23" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B23" s="2"/>
-      <c r="C23" s="10">
+      <c r="C23" s="12">
         <f>D23&amp;" " &amp;$E$4&amp;" "&amp;E23&amp;" "</f>
       </c>
       <c r="D23" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F23" s="6"/>
+        <v>69</v>
+      </c>
+      <c r="F23" s="8"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -1714,7 +1745,7 @@
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
-      <c r="O24" s="1"/>
+      <c r="O24" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="1"/>
@@ -1731,11 +1762,11 @@
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
-      <c r="O25" s="1"/>
+      <c r="O25" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="2"/>
@@ -1750,15 +1781,15 @@
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
-      <c r="O26" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75" customFormat="1" s="4">
+      <c r="O26" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="30.75" customFormat="1" s="5">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>70</v>
+      <c r="C27" s="6" t="s">
+        <v>3</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>4</v>
@@ -1766,41 +1797,47 @@
       <c r="E27" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F27" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G27" s="5"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
+      <c r="F27" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H27" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="I27" s="17" t="s">
+        <v>74</v>
+      </c>
       <c r="J27" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>11</v>
       </c>
       <c r="L27" s="2"/>
-      <c r="M27" s="5" t="s">
+      <c r="M27" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N27" s="5" t="s">
+      <c r="N27" s="6" t="s">
         <v>14</v>
       </c>
       <c r="O27" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75" customFormat="1" s="5">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F28" s="6"/>
+      <c r="E28" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F28" s="8"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
-      <c r="J28" s="7" t="s">
-        <v>73</v>
+      <c r="J28" s="9" t="s">
+        <v>77</v>
       </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
@@ -1810,7 +1847,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="2"/>
@@ -1818,7 +1855,7 @@
         <v>23</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="2"/>
@@ -1829,8 +1866,8 @@
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
-      <c r="O29" s="1" t="s">
-        <v>76</v>
+      <c r="O29" s="4" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/iba/docs/escalation actions worksheet.xlsx
+++ b/iba/docs/escalation actions worksheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Bible_study_projects\iba\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E55F68-F4D0-46D7-B92D-91F44D2B0BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9080CD6-ABDF-43C4-8324-A643C61CB10F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,14 +34,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="108">
   <si>
     <t xml:space="preserve">iba\app\ps\Escalation.ps1 -action update -Id </t>
   </si>
   <si>
-    <t xml:space="preserve"> -ResolutionKind DecisionRequired -NextAction approved -AssignedTo Claude   -Comment ' noted' </t>
-  </si>
-  <si>
     <t>Escalation tool</t>
   </si>
   <si>
@@ -342,9 +339,6 @@
     <t>correction</t>
   </si>
   <si>
-    <t>corrected title</t>
-  </si>
-  <si>
     <t>original title had a typo</t>
   </si>
   <si>
@@ -360,7 +354,10 @@
     <t>proceed</t>
   </si>
   <si>
-    <t>this report is still not complete. I suspect the data comes straight from the DB schema. However, the report should merge the data and the DB schema extract and show the comparison. I can spot some that will show discrepancies. This applies for both the table level and column level data and applies to both IBA and Bible research under item 1337</t>
+    <t>Can you verify that this block is now removed. Done through the developer mode work.  If so, you can push this through to ready for approval and sign off</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -ResolutionKind DecisionRequired -NextAction approved -AssignedTo Claude   -Comment ' processed configs' </t>
   </si>
 </sst>
 </file>
@@ -480,7 +477,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -523,25 +520,18 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -855,7 +845,7 @@
     <col min="3" max="3" width="31.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="22" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -869,7 +859,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2"/>
       <c r="E1" s="2"/>
@@ -896,7 +886,7 @@
     </row>
     <row r="3" spans="1:19" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2"/>
       <c r="E3" s="2"/>
@@ -912,58 +902,58 @@
     <row r="4" spans="1:19" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="G4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="O4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="P4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="P4" s="10" t="s">
+      <c r="Q4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Q4" s="10" t="s">
+      <c r="R4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="R4" s="10" t="s">
+      <c r="S4" s="10" t="s">
         <v>20</v>
-      </c>
-      <c r="S4" s="10" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:19" s="1" customFormat="1" ht="87" customHeight="1" x14ac:dyDescent="0.25">
@@ -972,73 +962,73 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="18"/>
+      <c r="F5" s="17"/>
       <c r="G5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="Q5" s="11" t="s">
+      <c r="R5" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="R5" s="11" t="s">
+      <c r="S5" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="S5" s="11" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:19" s="1" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="C6" s="3" t="str">
         <f>D6&amp;" " &amp;$E$4&amp;" "&amp;E6&amp;" "  &amp;$G$4&amp;" '"&amp;G6&amp;"' "&amp;$H$4&amp;" "&amp;H6&amp;" " &amp;$I$4&amp;" "&amp;I6&amp; " " &amp;$K$4 &amp; " " &amp;K6 &amp; " " &amp;$M$4&amp;" '" &amp; M6 &amp; "' " &amp;$N$4&amp;" '" &amp; N6 &amp;"' "</f>
         <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action raise -Question 'Schema overview report' -ResolutionKind DecisionRequired -Type issue -AssignedTo Researcher -Comment 'There is no schema overview report for Bible_research_DB' -Context '' </v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="17"/>
+      <c r="G6" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N6" s="7"/>
       <c r="O6" s="2"/>
@@ -1046,35 +1036,35 @@
     <row r="7" spans="1:19" s="1" customFormat="1" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" s="3" t="str">
         <f>D7&amp;" " &amp;$E$4&amp;" "&amp;E7&amp;" "  &amp;$G$4&amp;" ' "&amp;G7&amp;" ' "&amp;$H$4&amp;" "&amp;H7&amp;" " &amp;$I$4&amp;" "&amp;I7&amp; " " &amp;$K$4 &amp; " " &amp;K7 &amp; " " &amp;$M$4&amp;" ' " &amp; M7 &amp; " ' " &amp;$N$4&amp;" ' " &amp; N7 &amp;" ' "</f>
         <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action raise -Question ' config table purpose ' -ResolutionKind DecisionRequired -Type task -AssignedTo Researcher -Comment ' Add two additional config entries for each cfg table: a)a) purpose - the purpose of this table is to …....why does it exist, what does it do, the scope it covers b) success - what must this table have to be successful ' -Context '  ' </v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="17"/>
+      <c r="G7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="18"/>
-      <c r="G7" s="7" t="s">
+      <c r="I7" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N7" s="7"/>
       <c r="O7" s="2"/>
@@ -1082,38 +1072,38 @@
     <row r="8" spans="1:19" s="1" customFormat="1" ht="87" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C8" s="3" t="str">
         <f>D8&amp;" " &amp;$E$4&amp;" "&amp;E8&amp;" "  &amp;$G$4&amp;" '"&amp;G8&amp;"' "&amp;$H$4&amp;" "&amp;H8&amp;" " &amp;$I$4&amp;" "&amp;I8&amp; " " &amp;$K$4 &amp; " " &amp;K8 &amp; " " &amp;$M$4&amp;" '" &amp; M8 &amp; "' " &amp;$N$4&amp;" '" &amp; N8 &amp;"' "</f>
         <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action raise -Question 'title' -ResolutionKind DecisionRequired -Type notice -AssignedTo Researcher -Comment 'assigment' -Context 'more info' </v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="17"/>
+      <c r="G8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="7" t="s">
+      <c r="I8" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O8" s="2"/>
     </row>
@@ -1143,240 +1133,240 @@
     </row>
     <row r="11" spans="1:19" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="C11" s="3" t="str">
         <f>D11&amp;" " &amp;$E$4&amp;" "&amp;E11&amp;" " &amp;$F$4&amp;" "&amp;F11&amp;" "  &amp;$H$4&amp;" "&amp;H11&amp;" " &amp;$J$4&amp;" "&amp;J11&amp; " " &amp;$K$4 &amp; " " &amp;K11 &amp; " " &amp;$L$4 &amp; " " &amp;L11 &amp; " " &amp;$M$4&amp;" ' " &amp; M11 &amp; " ' " &amp;$N$4&amp;" ' " &amp; N11 &amp;" ' "</f>
         <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action update -Id 1320 -ResolutionKind DecisionRequired -NextAction review -AssignedTo Claude -State in-progress -Comment ' proceed ' -Context '  ' </v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="19">
+        <v>48</v>
+      </c>
+      <c r="F11" s="18">
         <v>1320</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="L11" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="M11" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N11" s="7"/>
     </row>
     <row r="12" spans="1:19" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C12" s="3" t="str">
         <f>D12&amp;" " &amp;$E$4&amp;" "&amp;E12&amp;" " &amp;$F$4&amp;" "&amp;F12&amp;" "  &amp;$H$4&amp;" "&amp;H12&amp;" " &amp;$J$4&amp;" "&amp;J12&amp; " " &amp;$K$4 &amp; " " &amp;K12 &amp; " " &amp;$L$4 &amp; " " &amp;L12 &amp; " " &amp;$M$4&amp;" '" &amp; M12 &amp; "' " &amp;$N$4&amp;" '" &amp; N12 &amp;"' "</f>
-        <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action update -Id 1306 -ResolutionKind DecisionRequired -NextAction revise -AssignedTo Claude -State in-progress -Comment 'this report is still not complete. I suspect the data comes straight from the DB schema. However, the report should merge the data and the DB schema extract and show the comparison. I can spot some that will show discrepancies. This applies for both the table level and column level data and applies to both IBA and Bible research under item 1337' -Context '' </v>
+        <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action update -Id 1327 -ResolutionKind DecisionRequired -NextAction revise -AssignedTo Claude -State in-progress -Comment 'Can you verify that this block is now removed. Done through the developer mode work.  If so, you can push this through to ready for approval and sign off' -Context '' </v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" s="19">
-        <v>1306</v>
+        <v>48</v>
+      </c>
+      <c r="F12" s="18">
+        <v>1327</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="L12" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="M12" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N12" s="7"/>
     </row>
     <row r="13" spans="1:19" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13" s="3" t="str">
         <f>D13&amp;" " &amp;$E$4&amp;" "&amp;E13&amp;" " &amp;$F$4&amp;" "&amp;F13&amp;" "  &amp;$H$4&amp;" "&amp;H13&amp;" " &amp;$J$4&amp;" "&amp;J13&amp; " " &amp;$K$4 &amp; " " &amp;K13 &amp; " "&amp;$L$4 &amp; " " &amp;L13 &amp; " " &amp;$M$4&amp;" '" &amp; M13 &amp; "' " &amp;$N$4&amp;" '" &amp; N13 &amp;"' " &amp;$O$4 &amp; " '"&amp; O13 &amp;"'"</f>
         <v>iba\app\ps\Escalation.ps1 -action update -Id 921 -ResolutionKind DecisionRequired -NextAction ready_for_approval -AssignedTo Researcher -State in-progress -Comment 'Set to ready for approval' -Context '' -Resolution 'Resolution required'</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="19">
+        <v>48</v>
+      </c>
+      <c r="F13" s="18">
         <v>921</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="7" t="s">
         <v>54</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>55</v>
       </c>
       <c r="N13" s="7"/>
       <c r="O13" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C14" s="3" t="str">
         <f>D14&amp;" " &amp;$E$4&amp;" "&amp;E14&amp;" " &amp;$F$4&amp;" "&amp;F14&amp;" "  &amp;$H$4&amp;" "&amp;H14&amp;" " &amp;$J$4&amp;" "&amp;J14&amp; " " &amp;$K$4 &amp; " " &amp;K14 &amp; " " &amp;$M$4&amp;" ' " &amp; M14 &amp; " ' "</f>
-        <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action update -Id 1309 -ResolutionKind DecisionRequired -NextAction approved -AssignedTo Claude -Comment ' noted ' </v>
+        <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action update -Id 1327 -ResolutionKind DecisionRequired -NextAction approved -AssignedTo Claude -Comment ' noted ' </v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F14" s="13">
-        <v>1309</v>
+        <v>1327</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N14" s="7"/>
     </row>
     <row r="15" spans="1:19" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C15" s="3" t="str">
         <f>D15&amp;" " &amp;$E$4&amp;" "&amp;E15&amp;" " &amp;$F$4&amp;" "&amp;F15&amp;" "  &amp;$H$4&amp;" "&amp;H15&amp;" " &amp;$J$4&amp;" "&amp;J15&amp; " " &amp;$K$4 &amp; " " &amp;K15 &amp; " "&amp;$L$4 &amp; " " &amp;L15 &amp; " " &amp;$M$4&amp;" '" &amp; M15 &amp; "' " &amp;$N$4&amp;" '" &amp; N15 &amp;"' " &amp;$O$4 &amp; " '"&amp; O15 &amp;"'"</f>
         <v>iba\app\ps\Escalation.ps1 -action update -Id 9 -ResolutionKind  -NextAction reject -AssignedTo Claude -State supersede -Comment 'substantial work has gone into governance, and I am not planning to do a another full sweep of governance' -Context '' -Resolution ''</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="19">
+        <v>48</v>
+      </c>
+      <c r="F15" s="18">
         <v>9</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L15" s="2" t="s">
+      <c r="M15" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>62</v>
       </c>
       <c r="N15" s="7"/>
     </row>
     <row r="16" spans="1:19" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C16" s="3" t="str">
         <f>D16&amp;" " &amp;$E$4&amp;" "&amp;E16&amp;" " &amp;$F$4&amp;" "&amp;F16&amp;" "  &amp;$H$4&amp;" "&amp;H16&amp;" " &amp;$J$4&amp;" "&amp;J16&amp; " " &amp;$K$4 &amp; " " &amp;K16 &amp; " "&amp;$L$4 &amp; " " &amp;L16 &amp; " " &amp;$M$4&amp;" '" &amp; M16 &amp; "' " &amp;$N$4&amp;" '" &amp; N16 &amp;"' " &amp;$O$4 &amp; " '"&amp; O16 &amp;"'"</f>
         <v>iba\app\ps\Escalation.ps1 -action update -Id 1343 -ResolutionKind DecisionRequired -NextAction reject -AssignedTo Claude -State withdraw -Comment 'not approved, to be redesigned' -Context '' -Resolution ''</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="19">
+        <v>48</v>
+      </c>
+      <c r="F16" s="18">
         <v>1343</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="M16" s="7" t="s">
         <v>63</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>64</v>
       </c>
       <c r="N16" s="7"/>
     </row>
     <row r="17" spans="1:15" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C17" s="3" t="str">
         <f>D17&amp;" " &amp;$E$4&amp;" "&amp;E17&amp;" " &amp;$F$4&amp;" "&amp;F17&amp;" "  &amp;IF(J17="","",$J$4&amp;" "&amp;J17&amp;" ") &amp;$K$4 &amp; " " &amp;K17 &amp; " "&amp;$L$4 &amp; " " &amp;L17 &amp; " " &amp;$M$4&amp;" '" &amp; M17 &amp; "' " &amp;$N$4&amp;" '" &amp; N17 &amp;"' " &amp;$O$4 &amp; " '"&amp; O17 &amp;"'"</f>
         <v>iba\app\ps\Escalation.ps1 -action update -Id 1022 -AssignedTo Researcher -State on-hold -Comment 'set to on hold' -Context '' -Resolution ''</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="19">
+        <v>48</v>
+      </c>
+      <c r="F17" s="18">
         <v>1022</v>
       </c>
       <c r="G17" s="2"/>
@@ -1384,13 +1374,13 @@
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M17" s="7" t="s">
         <v>66</v>
-      </c>
-      <c r="M17" s="7" t="s">
-        <v>67</v>
       </c>
       <c r="N17" s="7"/>
     </row>
@@ -1408,7 +1398,7 @@
     </row>
     <row r="19" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C19" s="2"/>
       <c r="E19" s="2"/>
@@ -1435,19 +1425,19 @@
     </row>
     <row r="21" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C21" s="3" t="str">
         <f>D21&amp;" " &amp;$E$4&amp;" "&amp;E21&amp;" " &amp;$F$4 &amp; " " &amp;F21</f>
         <v>iba\app\ps\Escalation.ps1 -action History -Id 851</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F21" s="20">
+        <v>70</v>
+      </c>
+      <c r="F21" s="19">
         <v>851</v>
       </c>
       <c r="G21" s="2"/>
@@ -1472,7 +1462,7 @@
     </row>
     <row r="23" spans="1:15" s="1" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="3" t="str">
@@ -1480,12 +1470,12 @@
         <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action List </v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F23" s="18"/>
+        <v>72</v>
+      </c>
+      <c r="F23" s="17"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -1522,7 +1512,7 @@
     </row>
     <row r="26" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C26" s="2"/>
       <c r="E26" s="2"/>
@@ -1538,37 +1528,37 @@
     <row r="27" spans="1:15" s="1" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F27" s="17" t="s">
+      <c r="H27" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H27" s="9" t="s">
+      <c r="I27" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="I27" s="9" t="s">
-        <v>77</v>
-      </c>
       <c r="J27" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
@@ -1580,28 +1570,28 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F28" s="21" t="s">
+      <c r="G28" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="H28" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="I28" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="J28" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="K28" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K28" s="3" t="s">
+      <c r="L28" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
@@ -1609,30 +1599,30 @@
     </row>
     <row r="29" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="C29" s="2" t="str">
         <f>D29&amp;" " &amp;$E$27&amp;" "&amp;E29&amp;" " &amp;$F$27&amp;" "&amp;F29&amp;" "  &amp;$H$27&amp;" "&amp;H29&amp;" " &amp;$I$27&amp;" "&amp;I29&amp;" " &amp;IF(L29="","",$L$27&amp;" '"&amp;L29&amp;"' ")</f>
         <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action AnswerRun -RunId RUN-20260829_063456_930-CONFIGMAINT -Decision Approve -AnsweredBy Researcher </v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E29" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="F29" s="17" t="s">
-        <v>88</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J29" s="2"/>
       <c r="L29" s="2"/>
@@ -1641,149 +1631,150 @@
     </row>
     <row r="30" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C30" t="str">
         <f>D30&amp;" " &amp;$E$27&amp;" "&amp;E30&amp;" " &amp;$G$27&amp;" "&amp;G30&amp;" "  &amp;$I$27&amp;" "&amp;I30&amp;" " &amp;$J$27&amp;" '"&amp;J30&amp;"' "</f>
         <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action ResolveSelfCorrectable -Id 1300 -AnsweredBy Claude -Resolution 'usage error, not a code defect -- retried immediately with the missing flag included' </v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G30" s="2">
         <v>1300</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C31" t="str">
         <f>D31&amp;" " &amp;$E$27&amp;" "&amp;E31&amp;" " &amp;$G$27&amp;" "&amp;G31&amp;" "  &amp;$I$27&amp;" "&amp;I31&amp;" " &amp;$K$27&amp;" '"&amp;K31&amp;"' "</f>
         <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action EscalateToDecision -Id 812 -AnsweredBy Claude -Tried 'widened the retry window, but the limit is a design choice' </v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G31" s="2">
         <v>812</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="2:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="F33" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F33" s="17" t="s">
-        <v>8</v>
-      </c>
       <c r="G33" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I33" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="J33" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="K33" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K33" s="2" t="s">
+      <c r="L33" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O33" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L33" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N33" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="34" spans="2:15" ht="90" x14ac:dyDescent="0.25">
-      <c r="F34" s="21" t="s">
+      <c r="F34" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="H34" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="I34" s="3" t="s">
+      <c r="L34" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="L34" s="3" t="s">
+      <c r="M34" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="M34" s="3" t="s">
+      <c r="O34" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="O34" s="3" t="s">
+    </row>
+    <row r="35" spans="2:15" ht="75" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C35" s="1" t="str">
+        <f>D35&amp;" " &amp;$E$33&amp;" "&amp;E35&amp;" " &amp;$F$33&amp;" "&amp;F35&amp;" "  &amp;$G$33&amp;" '"&amp;G35&amp;"' " &amp;$H$33&amp;" "&amp;H35&amp;" " &amp;$O$33&amp;" '"&amp;O35&amp;"' "</f>
+        <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action correction -Id 741 -ShortDescription '' -AnsweredBy Researcher -Comment 'original title had a typo' </v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="B35" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C35" t="str">
-        <f>D35&amp;" " &amp;$E$33&amp;" "&amp;E35&amp;" " &amp;$F$33&amp;" "&amp;F35&amp;" "  &amp;$G$33&amp;" '"&amp;G35&amp;"' " &amp;$H$33&amp;" "&amp;H35&amp;" " &amp;$O$33&amp;" '"&amp;O35&amp;"' "</f>
-        <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action correction -Id 741 -ShortDescription 'corrected title' -AnsweredBy Researcher -Comment 'original title had a typo' </v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E35" s="2" t="s">
+      <c r="F35" s="2">
+        <v>741</v>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="O35" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="F35" s="17">
-        <v>741</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1804,14 +1795,14 @@
         <v>0</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="C5">
-        <v>1281</v>
+        <v>1331</v>
       </c>
       <c r="D5" t="str">
-        <f t="shared" ref="D5:D23" si="0">A5&amp;C5&amp;B5</f>
-        <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action update -Id 1281 -ResolutionKind DecisionRequired -NextAction approved -AssignedTo Claude   -Comment ' noted' </v>
+        <f t="shared" ref="D5:D10" si="0">A5&amp;C5&amp;B5</f>
+        <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action update -Id 1331 -ResolutionKind DecisionRequired -NextAction approved -AssignedTo Claude   -Comment ' processed configs' </v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1819,14 +1810,14 @@
         <v>0</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="C6">
-        <v>1282</v>
+        <v>1332</v>
       </c>
       <c r="D6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action update -Id 1282 -ResolutionKind DecisionRequired -NextAction approved -AssignedTo Claude   -Comment ' noted' </v>
+        <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action update -Id 1332 -ResolutionKind DecisionRequired -NextAction approved -AssignedTo Claude   -Comment ' processed configs' </v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1834,14 +1825,14 @@
         <v>0</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="C7">
-        <v>1283</v>
+        <v>1333</v>
       </c>
       <c r="D7" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action update -Id 1283 -ResolutionKind DecisionRequired -NextAction approved -AssignedTo Claude   -Comment ' noted' </v>
+        <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action update -Id 1333 -ResolutionKind DecisionRequired -NextAction approved -AssignedTo Claude   -Comment ' processed configs' </v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1849,14 +1840,14 @@
         <v>0</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="C8">
-        <v>1284</v>
+        <v>1334</v>
       </c>
       <c r="D8" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action update -Id 1284 -ResolutionKind DecisionRequired -NextAction approved -AssignedTo Claude   -Comment ' noted' </v>
+        <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action update -Id 1334 -ResolutionKind DecisionRequired -NextAction approved -AssignedTo Claude   -Comment ' processed configs' </v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1864,18 +1855,30 @@
         <v>0</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="C9">
-        <v>1285</v>
+        <v>1335</v>
       </c>
       <c r="D9" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action update -Id 1285 -ResolutionKind DecisionRequired -NextAction approved -AssignedTo Claude   -Comment ' noted' </v>
+        <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action update -Id 1335 -ResolutionKind DecisionRequired -NextAction approved -AssignedTo Claude   -Comment ' processed configs' </v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="12"/>
+      <c r="A10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10">
+        <v>1337</v>
+      </c>
+      <c r="D10" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">iba\app\ps\Escalation.ps1 -action update -Id 1337 -ResolutionKind DecisionRequired -NextAction approved -AssignedTo Claude   -Comment ' processed configs' </v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B11" s="12"/>
